--- a/ValidationPartitions.xlsx
+++ b/ValidationPartitions.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initial" sheetId="1" r:id="R81e730f95fc94b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated_CV" sheetId="2" r:id="Rcb26c934930f4b07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOBO" sheetId="4" r:id="R5cbcc7fd92604762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initial" sheetId="1" r:id="Rd276360a6e474b00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated_CV" sheetId="2" r:id="R69ac97690b17470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOBO" sheetId="4" r:id="R432f3484f0b74f1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,10 +474,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>train</x:v>
+        <x:v>validation</x:v>
       </x:c>
       <x:c r="D13"/>
     </x:row>
@@ -486,10 +486,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>train</x:v>
+        <x:v>validation</x:v>
       </x:c>
       <x:c r="D14"/>
     </x:row>
@@ -498,10 +498,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>train</x:v>
+        <x:v>validation</x:v>
       </x:c>
       <x:c r="D15"/>
     </x:row>
@@ -510,7 +510,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>train</x:v>
@@ -522,10 +522,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>validation</x:v>
+        <x:v>train</x:v>
       </x:c>
       <x:c r="D17"/>
     </x:row>
@@ -534,10 +534,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>validation</x:v>
+        <x:v>train</x:v>
       </x:c>
       <x:c r="D18"/>
     </x:row>
@@ -546,10 +546,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>validation</x:v>
+        <x:v>train</x:v>
       </x:c>
       <x:c r="D19"/>
     </x:row>
@@ -604,7 +604,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E2" s="13" t="str">
-        <x:v>1; 2; 4; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 4; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F2" s="13" t="str">
         <x:v>3; 5; 6</x:v>
@@ -624,10 +624,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>1; 2; 3; 5; 6; 7; 8; 10; 11; 12; 13; 14; 15; 16; 17</x:v>
+        <x:v>1; 2; 3; 5; 6; 7; 8; 10; 11; 15; 16; 17; 18; 12; 13</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
-        <x:v>4; 9; 18</x:v>
+        <x:v>4; 9; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
@@ -644,10 +644,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 13; 15; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 16; 18; 13; 14</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>12; 14; 16</x:v>
+        <x:v>15; 17; 12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
@@ -664,10 +664,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 14; 16; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 17; 12; 14</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>13; 15; 17</x:v>
+        <x:v>16; 18; 13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
@@ -684,7 +684,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
         <x:v>1; 10; 11</x:v>
@@ -704,7 +704,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>1; 3; 4; 5; 6; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 3; 4; 5; 6; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
         <x:v>2; 7; 8</x:v>
@@ -724,10 +724,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
-        <x:v>1; 2; 3; 4; 6; 7; 8; 9; 10; 12; 13; 14; 15; 16; 18</x:v>
+        <x:v>1; 2; 3; 4; 6; 7; 8; 9; 10; 15; 16; 17; 18; 12; 14</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>5; 11; 17</x:v>
+        <x:v>5; 11; 13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
@@ -744,10 +744,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 11; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 11; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
-        <x:v>7; 10; 12</x:v>
+        <x:v>7; 10; 15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
@@ -764,10 +764,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>1; 2; 3; 5; 6; 7; 8; 10; 11; 12; 13; 14; 15; 16; 17</x:v>
+        <x:v>1; 2; 3; 5; 6; 7; 8; 10; 11; 15; 16; 17; 18; 12; 13</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
-        <x:v>4; 9; 18</x:v>
+        <x:v>4; 9; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="50" customHeight="1">
@@ -784,10 +784,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
-        <x:v>3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 15; 16; 17; 18</x:v>
+        <x:v>3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:v>1; 2; 14</x:v>
+        <x:v>1; 2; 17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="50" customHeight="1">
@@ -804,10 +804,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 7; 9; 10; 11; 12; 13; 14; 15; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 7; 9; 10; 11; 15; 16; 17; 18; 13; 14</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>6; 8; 16</x:v>
+        <x:v>6; 8; 12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="50" customHeight="1">
@@ -824,10 +824,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 12; 14; 16; 17; 18</x:v>
+        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 15; 17; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>3; 13; 15</x:v>
+        <x:v>3; 16; 18</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="50" customHeight="1">
@@ -844,7 +844,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 8; 10; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 8; 10; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
         <x:v>7; 9; 11</x:v>
@@ -864,10 +864,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>1; 2; 3; 5; 6; 7; 8; 9; 11; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 5; 6; 7; 8; 9; 11; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:v>4; 10; 12</x:v>
+        <x:v>4; 10; 15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="50" customHeight="1">
@@ -884,10 +884,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 14; 15; 18</x:v>
+        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 17; 18; 14</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
-        <x:v>1; 16; 17</x:v>
+        <x:v>1; 12; 13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="50" customHeight="1">
@@ -904,10 +904,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>1; 3; 4; 5; 7; 8; 9; 10; 11; 12; 13; 15; 16; 17; 18</x:v>
+        <x:v>1; 3; 4; 5; 7; 8; 9; 10; 11; 15; 16; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
-        <x:v>2; 6; 14</x:v>
+        <x:v>2; 6; 17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="50" customHeight="1">
@@ -924,10 +924,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
-        <x:v>1; 2; 3; 4; 6; 7; 9; 10; 11; 12; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 6; 7; 9; 10; 11; 15; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
-        <x:v>5; 8; 13</x:v>
+        <x:v>5; 8; 16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="50" customHeight="1">
@@ -944,10 +944,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 14; 16; 17</x:v>
+        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 17; 12; 13</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
-        <x:v>3; 15; 18</x:v>
+        <x:v>3; 18; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="50" customHeight="1">
@@ -964,10 +964,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>1; 2; 3; 6; 7; 8; 9; 10; 11; 12; 13; 14; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 6; 7; 8; 9; 10; 11; 15; 16; 17; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
-        <x:v>4; 5; 15</x:v>
+        <x:v>4; 5; 18</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="50" customHeight="1">
@@ -984,10 +984,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 9; 10; 11; 13; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 9; 10; 11; 16; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
-        <x:v>8; 12; 14</x:v>
+        <x:v>8; 15; 17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="50" customHeight="1">
@@ -1004,10 +1004,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 11; 12; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 11; 15; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
-        <x:v>3; 10; 13</x:v>
+        <x:v>3; 10; 16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="50" customHeight="1">
@@ -1024,10 +1024,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 8; 10; 11; 12; 13; 14; 15; 16; 17</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 8; 10; 11; 15; 16; 17; 18; 12; 13</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
-        <x:v>7; 9; 18</x:v>
+        <x:v>7; 9; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="50" customHeight="1">
@@ -1044,10 +1044,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
-        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 12; 13; 14; 15; 17; 18</x:v>
+        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 15; 16; 17; 18; 13; 14</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
-        <x:v>1; 11; 16</x:v>
+        <x:v>1; 11; 12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="50" customHeight="1">
@@ -1064,10 +1064,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
-        <x:v>1; 3; 4; 5; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 18</x:v>
+        <x:v>1; 3; 4; 5; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 14</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
-        <x:v>2; 6; 17</x:v>
+        <x:v>2; 6; 13</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="50" customHeight="1">
@@ -1084,7 +1084,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 7; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 7; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
         <x:v>6; 8; 9</x:v>
@@ -1104,7 +1104,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>3; 4; 6; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>3; 4; 6; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>1; 2; 5</x:v>
@@ -1124,10 +1124,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E28" s="13" t="str">
-        <x:v>1; 2; 3; 5; 6; 7; 8; 9; 10; 11; 12; 14; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 5; 6; 7; 8; 9; 10; 11; 15; 17; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
-        <x:v>4; 13; 15</x:v>
+        <x:v>4; 16; 18</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="50" customHeight="1">
@@ -1144,10 +1144,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E29" s="13" t="str">
-        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 13; 14; 15; 17; 18</x:v>
+        <x:v>1; 2; 4; 5; 6; 7; 8; 9; 10; 11; 16; 17; 18; 13; 14</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
-        <x:v>3; 12; 16</x:v>
+        <x:v>3; 15; 12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="50" customHeight="1">
@@ -1164,10 +1164,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 12; 13; 15; 16; 17</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 15; 16; 18; 12; 13</x:v>
       </x:c>
       <x:c r="F30" s="13" t="str">
-        <x:v>11; 14; 18</x:v>
+        <x:v>11; 17; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="50" customHeight="1">
@@ -1184,10 +1184,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E31" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 11; 12; 13; 14; 15; 16; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 11; 15; 16; 17; 18; 12; 14</x:v>
       </x:c>
       <x:c r="F31" s="13" t="str">
-        <x:v>7; 10; 17</x:v>
+        <x:v>7; 10; 13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1195,7 +1195,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1241,7 +1241,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="13" t="str">
-        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F2" s="13" t="str">
         <x:v>1</x:v>
@@ -1261,10 +1261,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>1; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 18</x:v>
+        <x:v>1; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 14</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
-        <x:v>2; 17</x:v>
+        <x:v>2; 13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
@@ -1281,7 +1281,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>1; 2; 5; 6; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 5; 6; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
         <x:v>3; 4</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>1; 2; 3; 4; 6; 7; 8; 9; 10; 11; 12; 13; 14; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 6; 7; 8; 9; 10; 11; 15; 16; 17; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>5; 15</x:v>
+        <x:v>5; 18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
@@ -1321,7 +1321,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 7; 8; 9; 10; 11; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 7; 8; 9; 10; 11; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
         <x:v>6</x:v>
@@ -1341,10 +1341,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 10; 11; 12; 13; 14; 15; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 8; 9; 10; 11; 15; 16; 17; 18; 13; 14</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:v>7; 16</x:v>
+        <x:v>7; 12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="50" customHeight="1">
@@ -1361,10 +1361,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 10; 11; 12; 13; 14; 15; 16; 17</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 10; 11; 15; 16; 17; 18; 12; 13</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>8; 9; 18</x:v>
+        <x:v>8; 9; 14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
@@ -1381,7 +1381,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 12; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 15; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>10; 11</x:v>
@@ -1401,10 +1401,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 13; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 16; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="50" customHeight="1">
@@ -1421,10 +1421,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 14; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 17; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="50" customHeight="1">
@@ -1441,10 +1441,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 15; 16; 17; 18</x:v>
+        <x:v>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 15; 16; 18; 12; 13; 14</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ValidationPartitions.xlsx
+++ b/ValidationPartitions.xlsx
@@ -125,9 +125,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +177,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
